--- a/data/trans_dic/P0902-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P0902-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejó de hacer algunas tareas por problemas físicos</t>
+          <t>Población que dejó de hacer algunas tareas por problemas físicos (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,91</t>
+          <t>1,21; 4,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,45</t>
+          <t>1,49; 4,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,6</t>
+          <t>0,71; 3,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,58</t>
+          <t>2,74; 6,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 7,03</t>
+          <t>2,56; 6,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,1</t>
+          <t>1,69; 4,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 9,07</t>
+          <t>1,39; 7,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,66</t>
+          <t>2,16; 4,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,09</t>
+          <t>2,41; 4,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,66</t>
+          <t>1,41; 3,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,88</t>
+          <t>0,71; 3,67</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,05</t>
+          <t>1,5; 3,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,94</t>
+          <t>2,01; 4,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,32</t>
+          <t>2,23; 5,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 11,45</t>
+          <t>4,5; 11,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 9,13</t>
+          <t>5,12; 9,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 6,93</t>
+          <t>3,36; 7,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,55; 7,4</t>
+          <t>3,55; 7,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,14</t>
+          <t>2,65; 7,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 5,86</t>
+          <t>3,46; 6,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,33</t>
+          <t>3,02; 5,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 5,78</t>
+          <t>3,35; 5,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,01; 7,81</t>
+          <t>4,04; 7,96</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,57</t>
+          <t>3,2; 6,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,32; 8,12</t>
+          <t>4,31; 8,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 6,04</t>
+          <t>2,78; 5,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,76; 9,41</t>
+          <t>4,65; 9,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,47; 10,77</t>
+          <t>6,54; 10,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,82; 13,92</t>
+          <t>9,01; 13,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,74; 9,88</t>
+          <t>5,61; 9,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,47; 12,74</t>
+          <t>8,31; 12,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,37; 8,13</t>
+          <t>5,22; 8,09</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,15; 10,27</t>
+          <t>7,2; 10,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,41</t>
+          <t>4,7; 7,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,06; 10,29</t>
+          <t>7,14; 10,17</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 9,2</t>
+          <t>4,78; 9,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,85; 10,64</t>
+          <t>5,89; 10,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,09; 12,03</t>
+          <t>6,96; 11,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 14,31</t>
+          <t>4,15; 13,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,98; 16,08</t>
+          <t>10,1; 15,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,49; 18,94</t>
+          <t>12,38; 18,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,14; 15,51</t>
+          <t>10,21; 15,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,09; 17,45</t>
+          <t>12,12; 17,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,13; 11,94</t>
+          <t>7,98; 11,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,77; 13,69</t>
+          <t>9,82; 13,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,17; 12,68</t>
+          <t>9,19; 12,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,57; 14,35</t>
+          <t>7,38; 14,64</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,51; 17,56</t>
+          <t>10,29; 17,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,58; 19,57</t>
+          <t>12,45; 19,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,53; 16,04</t>
+          <t>9,11; 15,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,16; 22,5</t>
+          <t>15,9; 22,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,28; 19,56</t>
+          <t>11,77; 19,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,56; 31,91</t>
+          <t>23,16; 32,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,96; 28,18</t>
+          <t>19,66; 27,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,69; 24,96</t>
+          <t>19,82; 25,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,42; 17,24</t>
+          <t>12,11; 17,22</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,95; 24,6</t>
+          <t>18,91; 24,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,34; 21,03</t>
+          <t>15,29; 20,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,67; 23,03</t>
+          <t>18,74; 23,16</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,57; 21,02</t>
+          <t>12,66; 21,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,2; 29,57</t>
+          <t>18,35; 29,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,67; 20,79</t>
+          <t>12,77; 21,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,79; 20,27</t>
+          <t>13,92; 20,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,79; 34,33</t>
+          <t>24,79; 34,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,12; 42,45</t>
+          <t>32,42; 42,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,67; 37,8</t>
+          <t>27,21; 37,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,69; 29,39</t>
+          <t>8,16; 29,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,2; 26,83</t>
+          <t>20,33; 26,81</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26,98; 34,58</t>
+          <t>27,32; 34,37</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21,86; 28,5</t>
+          <t>21,86; 28,49</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,16; 23,64</t>
+          <t>9,16; 23,53</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,78; 40,4</t>
+          <t>27,3; 40,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38,03; 51,5</t>
+          <t>37,98; 51,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,81; 38,75</t>
+          <t>28,34; 38,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27,77; 37,01</t>
+          <t>28,06; 36,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>37,5; 48,28</t>
+          <t>36,67; 48,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,68; 65,01</t>
+          <t>54,6; 64,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,37; 59,35</t>
+          <t>48,51; 59,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51,41; 58,39</t>
+          <t>51,11; 58,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>34,79; 43,88</t>
+          <t>35,28; 43,57</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49,52; 57,87</t>
+          <t>49,87; 57,94</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41,76; 50,11</t>
+          <t>41,59; 50,16</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>42,96; 48,52</t>
+          <t>43,08; 48,27</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,29; 9,22</t>
+          <t>7,28; 9,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,97; 12,19</t>
+          <t>9,89; 12,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,28; 10,28</t>
+          <t>8,36; 10,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,29; 13,33</t>
+          <t>9,01; 13,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,37; 15,84</t>
+          <t>13,38; 15,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,73; 21,28</t>
+          <t>18,64; 21,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,5; 19,19</t>
+          <t>16,44; 19,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,43; 19,78</t>
+          <t>14,74; 19,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,73; 12,26</t>
+          <t>10,69; 12,26</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14,61; 16,43</t>
+          <t>14,78; 16,42</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12,75; 14,44</t>
+          <t>12,75; 14,43</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,06; 16,21</t>
+          <t>13,25; 16,4</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejó de hacer algunas tareas por problemas físicos</t>
+          <t>Población que dejó de hacer algunas tareas por problemas físicos (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6021; 19319</t>
+          <t>5964; 20237</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6630; 20195</t>
+          <t>6777; 21072</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2993; 15082</t>
+          <t>2982; 14258</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4435</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12722; 30744</t>
+          <t>12823; 30339</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11603; 30233</t>
+          <t>10994; 28709</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6610; 20189</t>
+          <t>6671; 19764</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5028; 28403</t>
+          <t>4350; 24368</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22165; 44829</t>
+          <t>20792; 44534</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21829; 44979</t>
+          <t>21350; 44110</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12457; 29799</t>
+          <t>11531; 29071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4751; 27646</t>
+          <t>5042; 26184</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12215; 29758</t>
+          <t>11019; 29199</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13712; 33929</t>
+          <t>13819; 33581</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13094; 31433</t>
+          <t>13154; 31520</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19693; 48477</t>
+          <t>19044; 46828</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30534; 57098</t>
+          <t>32021; 57498</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20435; 42201</t>
+          <t>20487; 42984</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19997; 41721</t>
+          <t>19986; 42111</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11380; 36471</t>
+          <t>13536; 36109</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47077; 79754</t>
+          <t>47079; 81797</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39012; 69082</t>
+          <t>39061; 69912</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37652; 66662</t>
+          <t>38715; 68602</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37501; 73011</t>
+          <t>37723; 74426</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>20621; 41983</t>
+          <t>20409; 41347</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29481; 55372</t>
+          <t>29414; 55171</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19074; 40401</t>
+          <t>18600; 39010</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25519; 50494</t>
+          <t>24943; 50721</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>44645; 74305</t>
+          <t>45085; 74598</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62587; 98843</t>
+          <t>63966; 98991</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37939; 65358</t>
+          <t>37099; 65294</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45951; 69098</t>
+          <t>45090; 69369</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>71392; 107948</t>
+          <t>69298; 107442</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>99453; 142953</t>
+          <t>100183; 142240</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61924; 98545</t>
+          <t>62470; 97583</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76128; 111015</t>
+          <t>76982; 109724</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24035; 47772</t>
+          <t>24837; 48141</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35937; 65366</t>
+          <t>36205; 65289</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45788; 77698</t>
+          <t>44955; 75687</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36712; 126877</t>
+          <t>36793; 123509</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>51478; 82906</t>
+          <t>52059; 81745</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>76970; 116701</t>
+          <t>76265; 112851</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>65811; 100648</t>
+          <t>66278; 99488</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>86117; 124277</t>
+          <t>86340; 124180</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>84102; 123514</t>
+          <t>82560; 121966</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>120250; 168536</t>
+          <t>120875; 167769</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>118815; 164237</t>
+          <t>118988; 165876</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>105128; 229471</t>
+          <t>118009; 234085</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>40632; 67918</t>
+          <t>39811; 65758</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>54008; 84043</t>
+          <t>53468; 83900</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45543; 76659</t>
+          <t>43531; 76032</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90717; 126271</t>
+          <t>89209; 125916</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>49613; 79019</t>
+          <t>47567; 76872</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>105056; 142264</t>
+          <t>103289; 143019</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99162; 140016</t>
+          <t>97668; 135828</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>107889; 136761</t>
+          <t>108597; 137631</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>98232; 136285</t>
+          <t>95779; 136129</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>165854; 215286</t>
+          <t>165546; 216906</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>149577; 204966</t>
+          <t>149057; 200350</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>207110; 255489</t>
+          <t>207881; 256821</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>36789; 61502</t>
+          <t>37054; 61951</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>59470; 91604</t>
+          <t>56852; 90042</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>42360; 69504</t>
+          <t>42680; 71036</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50577; 74369</t>
+          <t>51044; 74241</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>85013; 117746</t>
+          <t>85025; 117291</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>113702; 150264</t>
+          <t>114776; 149739</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>104521; 142799</t>
+          <t>102807; 141426</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>46794; 178800</t>
+          <t>49637; 177995</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>128358; 170478</t>
+          <t>129197; 170404</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>179062; 229533</t>
+          <t>181338; 228114</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>155679; 202967</t>
+          <t>155671; 202870</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>89363; 230530</t>
+          <t>89285; 229473</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>58302; 84791</t>
+          <t>57297; 85007</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>95027; 128661</t>
+          <t>94899; 128231</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>71462; 99585</t>
+          <t>72833; 99387</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>78393; 104475</t>
+          <t>79190; 104271</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>125231; 161198</t>
+          <t>122433; 160771</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>212710; 252893</t>
+          <t>212366; 252000</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>193551; 237504</t>
+          <t>194124; 239428</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>218682; 248400</t>
+          <t>217436; 247390</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>189164; 238597</t>
+          <t>191871; 236932</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>316323; 369682</t>
+          <t>318593; 370126</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>274409; 329308</t>
+          <t>273338; 329657</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>304039; 343370</t>
+          <t>304829; 341551</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>238988; 302230</t>
+          <t>238484; 303784</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>341647; 417602</t>
+          <t>338801; 417786</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>281101; 349067</t>
+          <t>283906; 351962</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>321017; 460924</t>
+          <t>311360; 457551</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>451936; 535285</t>
+          <t>452227; 533460</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>665859; 756351</t>
+          <t>662615; 760522</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>584959; 680069</t>
+          <t>582595; 673586</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>528351; 724086</t>
+          <t>539522; 725184</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>713886; 816233</t>
+          <t>711231; 815883</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1019635; 1146997</t>
+          <t>1031353; 1146398</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>884783; 1002133</t>
+          <t>884720; 1001150</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>929269; 1153476</t>
+          <t>943159; 1167569</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P0902-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P0902-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,1</t>
+          <t>1,12; 3,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,64</t>
+          <t>1,51; 4,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,4</t>
+          <t>0,73; 3,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 6,49</t>
+          <t>2,47; 6,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 6,67</t>
+          <t>2,73; 6,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,99</t>
+          <t>1,61; 5,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 7,78</t>
+          <t>2,26; 9,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,63</t>
+          <t>2,32; 4,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,99</t>
+          <t>2,52; 4,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,57</t>
+          <t>1,49; 3,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,67</t>
+          <t>1,05; 4,65</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,97</t>
+          <t>1,54; 3,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,89</t>
+          <t>1,96; 4,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,34</t>
+          <t>2,18; 5,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,5; 11,06</t>
+          <t>4,21; 9,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,12; 9,19</t>
+          <t>5,2; 9,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,36; 7,06</t>
+          <t>3,25; 6,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,55; 7,47</t>
+          <t>3,55; 7,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 7,07</t>
+          <t>3,34; 7,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 6,01</t>
+          <t>3,47; 5,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 5,4</t>
+          <t>3,07; 5,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,94</t>
+          <t>3,19; 5,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,96</t>
+          <t>4,37; 8,0</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,47</t>
+          <t>3,15; 6,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,31; 8,09</t>
+          <t>4,49; 8,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,83</t>
+          <t>2,8; 5,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 9,46</t>
+          <t>4,39; 8,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,54; 10,82</t>
+          <t>6,48; 10,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,01; 13,94</t>
+          <t>8,63; 13,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,61; 9,87</t>
+          <t>5,65; 9,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,31; 12,79</t>
+          <t>8,08; 12,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 8,09</t>
+          <t>5,26; 8,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,2; 10,22</t>
+          <t>7,21; 10,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,7; 7,33</t>
+          <t>4,73; 7,43</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 10,17</t>
+          <t>6,61; 9,74</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,78; 9,27</t>
+          <t>4,92; 9,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,89; 10,62</t>
+          <t>5,97; 10,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,96; 11,72</t>
+          <t>7,18; 11,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,15; 13,93</t>
+          <t>10,33; 15,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,1; 15,85</t>
+          <t>10,1; 15,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,38; 18,31</t>
+          <t>12,64; 18,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,21; 15,33</t>
+          <t>10,16; 15,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,12; 17,43</t>
+          <t>12,47; 16,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,98; 11,79</t>
+          <t>8,0; 11,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,82; 13,63</t>
+          <t>9,88; 13,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,19; 12,81</t>
+          <t>9,12; 12,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,38; 14,64</t>
+          <t>12,13; 15,5</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,29; 17,0</t>
+          <t>10,49; 17,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,45; 19,54</t>
+          <t>12,59; 19,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,11; 15,91</t>
+          <t>8,88; 15,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,9; 22,44</t>
+          <t>15,58; 21,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,77; 19,03</t>
+          <t>12,24; 19,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,16; 32,08</t>
+          <t>23,38; 31,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,66; 27,34</t>
+          <t>19,53; 27,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,82; 25,12</t>
+          <t>20,45; 25,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,11; 17,22</t>
+          <t>12,49; 17,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,91; 24,78</t>
+          <t>18,89; 25,02</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,29; 20,55</t>
+          <t>15,38; 20,58</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,74; 23,16</t>
+          <t>18,57; 22,79</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,66; 21,17</t>
+          <t>12,36; 20,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,35; 29,07</t>
+          <t>18,8; 29,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,77; 21,25</t>
+          <t>12,83; 20,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,92; 20,24</t>
+          <t>13,55; 19,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,79; 34,2</t>
+          <t>25,19; 34,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,42; 42,3</t>
+          <t>31,89; 42,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,21; 37,44</t>
+          <t>27,39; 37,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,16; 29,26</t>
+          <t>25,14; 31,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,33; 26,81</t>
+          <t>20,53; 26,7</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>27,32; 34,37</t>
+          <t>27,25; 34,48</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21,86; 28,49</t>
+          <t>21,79; 28,93</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,16; 23,53</t>
+          <t>20,5; 24,76</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>46,07%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,3; 40,5</t>
+          <t>28,18; 40,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37,98; 51,32</t>
+          <t>38,0; 50,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28,34; 38,67</t>
+          <t>27,85; 39,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28,06; 36,94</t>
+          <t>27,94; 37,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>36,67; 48,15</t>
+          <t>37,14; 48,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,6; 64,79</t>
+          <t>54,69; 65,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,51; 59,83</t>
+          <t>48,15; 59,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51,11; 58,16</t>
+          <t>51,82; 58,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>35,28; 43,57</t>
+          <t>35,46; 43,82</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49,87; 57,94</t>
+          <t>49,45; 58,08</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41,59; 50,16</t>
+          <t>41,71; 50,18</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>43,08; 48,27</t>
+          <t>43,31; 48,82</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,28; 9,27</t>
+          <t>7,31; 9,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,89; 12,2</t>
+          <t>9,89; 12,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,36; 10,37</t>
+          <t>8,32; 10,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,01; 13,24</t>
+          <t>11,4; 13,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,38; 15,79</t>
+          <t>13,43; 15,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,64; 21,4</t>
+          <t>18,55; 21,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,44; 19,0</t>
+          <t>16,32; 19,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,74; 19,81</t>
+          <t>18,61; 20,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,69; 12,26</t>
+          <t>10,71; 12,25</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14,78; 16,42</t>
+          <t>14,69; 16,43</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12,75; 14,43</t>
+          <t>12,64; 14,46</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,25; 16,4</t>
+          <t>15,37; 16,99</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12241</t>
+          <t>17735</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12241</t>
+          <t>17735</t>
         </is>
       </c>
     </row>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5964; 20237</t>
+          <t>5546; 19326</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6777; 21072</t>
+          <t>6845; 20598</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2982; 14258</t>
+          <t>3061; 16146</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2088,42 +2088,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12823; 30339</t>
+          <t>11544; 28408</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10994; 28709</t>
+          <t>11740; 28779</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6671; 19764</t>
+          <t>6357; 20479</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4350; 24368</t>
+          <t>8185; 35487</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20792; 44534</t>
+          <t>22268; 43774</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21350; 44110</t>
+          <t>22271; 44128</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11531; 29071</t>
+          <t>12156; 29578</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5042; 26184</t>
+          <t>8068; 35810</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30226</t>
+          <t>32057</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23490</t>
+          <t>25602</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53716</t>
+          <t>57659</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11019; 29199</t>
+          <t>11309; 28904</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13819; 33581</t>
+          <t>13460; 33291</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13154; 31520</t>
+          <t>12900; 31862</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19044; 46828</t>
+          <t>20092; 47514</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32021; 57498</t>
+          <t>32548; 57863</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20487; 42984</t>
+          <t>19825; 42188</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19986; 42111</t>
+          <t>20021; 41838</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13536; 36109</t>
+          <t>16698; 37937</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47079; 81797</t>
+          <t>47160; 79365</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39061; 69912</t>
+          <t>39748; 69247</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38715; 68602</t>
+          <t>36789; 65922</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37723; 74426</t>
+          <t>42753; 78181</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36375</t>
+          <t>37664</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>55804</t>
+          <t>62264</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92179</t>
+          <t>99928</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>20409; 41347</t>
+          <t>20123; 43079</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29414; 55171</t>
+          <t>30605; 57931</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18600; 39010</t>
+          <t>18728; 39278</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24943; 50721</t>
+          <t>27240; 53219</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>45085; 74598</t>
+          <t>44701; 73000</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63966; 98991</t>
+          <t>61297; 98450</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37099; 65294</t>
+          <t>37357; 65942</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45090; 69369</t>
+          <t>50270; 76119</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>69298; 107442</t>
+          <t>69883; 106257</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100183; 142240</t>
+          <t>100290; 143907</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62470; 97583</t>
+          <t>62906; 98842</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76982; 109724</t>
+          <t>82133; 121087</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>83378</t>
+          <t>91239</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>102899</t>
+          <t>107914</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>186277</t>
+          <t>199153</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24837; 48141</t>
+          <t>25519; 48197</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36205; 65289</t>
+          <t>36690; 63755</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44955; 75687</t>
+          <t>46376; 75564</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36793; 123509</t>
+          <t>72280; 111221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52059; 81745</t>
+          <t>52087; 81380</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>76265; 112851</t>
+          <t>77915; 116068</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66278; 99488</t>
+          <t>65932; 101370</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>86340; 124180</t>
+          <t>91817; 124679</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>82560; 121966</t>
+          <t>82759; 121615</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>120875; 167769</t>
+          <t>121610; 166930</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>118988; 165876</t>
+          <t>118097; 165213</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>118009; 234085</t>
+          <t>174209; 222483</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107179</t>
+          <t>112481</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>122917</t>
+          <t>140069</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>230096</t>
+          <t>252550</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>39811; 65758</t>
+          <t>40582; 65956</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>53468; 83900</t>
+          <t>54070; 83913</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43531; 76032</t>
+          <t>42437; 73415</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>89209; 125916</t>
+          <t>94965; 131301</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>47567; 76872</t>
+          <t>49438; 77717</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>103289; 143019</t>
+          <t>104263; 142126</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97668; 135828</t>
+          <t>97058; 135921</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>108597; 137631</t>
+          <t>124499; 155443</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>95779; 136129</t>
+          <t>98778; 137835</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>165546; 216906</t>
+          <t>165373; 219020</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>149057; 200350</t>
+          <t>149965; 200564</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>207881; 256821</t>
+          <t>226262; 277673</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61374</t>
+          <t>65879</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>114141</t>
+          <t>124922</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>175515</t>
+          <t>190801</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>37054; 61951</t>
+          <t>36156; 60465</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>56852; 90042</t>
+          <t>58225; 90625</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>42680; 71036</t>
+          <t>42904; 69804</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51044; 74241</t>
+          <t>54927; 79830</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>85025; 117291</t>
+          <t>86382; 117647</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>114776; 149739</t>
+          <t>112886; 151390</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>102807; 141426</t>
+          <t>103457; 139859</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>49637; 177995</t>
+          <t>110398; 138999</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>129197; 170404</t>
+          <t>130481; 169696</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>181338; 228114</t>
+          <t>180884; 228895</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>155671; 202870</t>
+          <t>155151; 206022</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>89285; 229473</t>
+          <t>173188; 209100</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>90973</t>
+          <t>100795</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>232036</t>
+          <t>255744</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>323009</t>
+          <t>356539</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>57297; 85007</t>
+          <t>59141; 84679</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>94899; 128231</t>
+          <t>94945; 127022</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>72833; 99387</t>
+          <t>71581; 100333</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>79190; 104271</t>
+          <t>86542; 115677</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>122433; 160771</t>
+          <t>123998; 160349</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>212366; 252000</t>
+          <t>212717; 253482</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>194124; 239428</t>
+          <t>192688; 237593</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>217436; 247390</t>
+          <t>240512; 272084</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>191871; 236932</t>
+          <t>192827; 238264</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>318593; 370126</t>
+          <t>315897; 371033</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>273338; 329657</t>
+          <t>274072; 329770</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>304829; 341551</t>
+          <t>335180; 377822</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>409505</t>
+          <t>440116</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>663528</t>
+          <t>734249</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1073033</t>
+          <t>1174366</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>238484; 303784</t>
+          <t>239433; 300171</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>338801; 417786</t>
+          <t>338802; 417195</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>283906; 351962</t>
+          <t>282523; 350229</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>311360; 457551</t>
+          <t>402461; 481057</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>452227; 533460</t>
+          <t>453785; 535608</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>662615; 760522</t>
+          <t>659330; 755598</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>582595; 673586</t>
+          <t>578553; 679771</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>539522; 725184</t>
+          <t>694929; 774617</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>711231; 815883</t>
+          <t>712708; 815514</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1031353; 1146398</t>
+          <t>1025490; 1146875</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>884720; 1001150</t>
+          <t>877351; 1003038</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>943159; 1167569</t>
+          <t>1116300; 1233820</t>
         </is>
       </c>
     </row>
